--- a/naver-place-crawler/results_health/해운대_헬스장.xlsx
+++ b/naver-place-crawler/results_health/해운대_헬스장.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="47" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>위헬스 장산역점</t>
+          <t>마블피트니스 헬스&amp;PT 해운대점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>wehealthjangsan@naver.com</t>
+          <t>hyoyoung0202@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1800-8273</t>
+          <t>0507-1384-2203</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산 해운대구 세실로 45 2층</t>
+          <t>부산 해운대구 해운대로469번길 8 2층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/wehealth_jangsan</t>
+          <t>https://blog.naver.com/hyoyoung0202</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5y91v</t>
+          <t>https://talk.naver.com/ct/w5tzkb</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>230</v>
+        <v>1461</v>
       </c>
       <c r="Q2" t="n">
-        <v>537</v>
+        <v>1413</v>
       </c>
       <c r="R2" t="n">
-        <v>767</v>
+        <v>2874</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1867376356</t>
+          <t>1774469002</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1867376356</t>
+          <t>https://m.place.naver.com/place/1774469002</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -662,34 +662,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>우노짐 헬스&amp;PT 마린시티점</t>
+          <t>마이애미짐 해운대점 24시헬스PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>unogym_1@naver.com</t>
+          <t>jeffkim94@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1419-1786</t>
+          <t>0507-1469-0064</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산 해운대구 마린시티2로 33 104동 B107-1호</t>
+          <t>부산 해운대구 해운대로 743 4층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/uno_gym_3</t>
+          <t>https://blog.naver.com/jeffkim94</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wpkopem</t>
+          <t>https://talk.naver.com/ct/w4n1kz</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>20</v>
+        <v>430</v>
       </c>
       <c r="Q3" t="n">
-        <v>6</v>
+        <v>956</v>
       </c>
       <c r="R3" t="n">
-        <v>26</v>
+        <v>1386</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2066839617</t>
+          <t>1040976831</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2066839617</t>
+          <t>https://m.place.naver.com/place/1040976831</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>마이애미짐 해운대점 24시헬스PT</t>
+          <t>멋짐 헬스 &amp; PT 마린시티점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>jeffkim94@naver.com</t>
+          <t>mutgym_@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1469-0064</t>
+          <t>0507-1380-2436</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산 해운대구 해운대로 743 4층</t>
+          <t>부산 해운대구 해운대해변로 163 현대베네시티 베네치아상가 지하1층 b101호, b101-2호, b101-5호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jeffkim94</t>
+          <t>https://blog.naver.com/mutgym_</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4n1kz</t>
+          <t>https://talk.naver.com/ct/wayqe12</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>425</v>
+        <v>77</v>
       </c>
       <c r="Q4" t="n">
-        <v>977</v>
+        <v>214</v>
       </c>
       <c r="R4" t="n">
-        <v>1402</v>
+        <v>291</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,56 +836,56 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1040976831</t>
+          <t>2055602485</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040976831</t>
+          <t>https://m.place.naver.com/place/2055602485</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>마블피트니스 헬스&amp;PT 해운대점</t>
+          <t>라이트짐 장산점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>hyoyoung0202@naver.com</t>
+          <t>busan91@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1384-2203</t>
+          <t>0507-1438-1740</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산 해운대구 해운대로469번길 8 2층</t>
+          <t>부산 해운대구 양운로 92 9층 라이트짐</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hyoyoung0202</t>
+          <t>https://open.kakao.com/o/sOS9sPTf</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5tzkb</t>
+          <t>https://talk.naver.com/ct/w45b6h</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1459</v>
+        <v>733</v>
       </c>
       <c r="Q5" t="n">
-        <v>1389</v>
+        <v>445</v>
       </c>
       <c r="R5" t="n">
-        <v>2848</v>
+        <v>1178</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +934,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1774469002</t>
+          <t>1418968603</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1774469002</t>
+          <t>https://m.place.naver.com/place/1418968603</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -956,39 +956,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>더플래닛짐 헬스&amp;PT 해운대 장산역점</t>
+          <t>쑥피트니스 해운대점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>theplanetgym@naver.com</t>
+          <t>ssookfitness_hd@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1310-5564</t>
+          <t>0507-1308-8420</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산 해운대구 세실로 77 성부빌딩 8층</t>
+          <t>부산 해운대구 해운대로774번길 11 4층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1992573620</t>
+          <t>https://blog.naver.com/ssookfitness_hd</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4gq28</t>
+          <t>https://talk.naver.com/ct/w4f0d6</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>191</v>
+        <v>393</v>
       </c>
       <c r="Q6" t="n">
-        <v>273</v>
+        <v>483</v>
       </c>
       <c r="R6" t="n">
-        <v>464</v>
+        <v>876</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1992573620</t>
+          <t>1246026577</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1992573620</t>
+          <t>https://m.place.naver.com/place/1246026577</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1054,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>멋짐 헬스 &amp; PT 마린시티점</t>
+          <t>마이애미짐 센텀점 24시헬스PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mutgym_@naver.com</t>
+          <t>miamigymnc@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1380-2436</t>
+          <t>0507-1319-8441</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산 해운대구 해운대해변로 163 현대베네시티 베네치아상가 지하1층 b101호, b101-2호, b101-5호</t>
+          <t>부산 해운대구 센텀중앙로 90 B1</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mutgym_</t>
+          <t>https://blog.naver.com/miamigymnc</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wayqe12</t>
+          <t>https://talk.naver.com/ct/w5v1em</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>71</v>
+        <v>302</v>
       </c>
       <c r="Q7" t="n">
-        <v>202</v>
+        <v>472</v>
       </c>
       <c r="R7" t="n">
-        <v>273</v>
+        <v>774</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,51 +1130,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2055602485</t>
+          <t>1160428762</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055602485</t>
+          <t>https://m.place.naver.com/place/1160428762</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>베스트피트니스 해운대 중동점</t>
+          <t>그래비티짐 해운대 장산점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>vastt_seomyeon@naver.com</t>
+          <t>acmilan0@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1321-1145</t>
+          <t>0507-1397-0149</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산 해운대구 좌동순환로 473 로데오아울렛 B동 4층</t>
+          <t>부산 해운대구 해운대로 802 웅신시네아트 A동 6층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/vastt_seomyeon</t>
+          <t>https://blog.naver.com/acmilan0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wwa9iy7</t>
+          <t>https://talk.naver.com/ct/w4o8qo</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>905</v>
+        <v>476</v>
       </c>
       <c r="Q8" t="n">
-        <v>1178</v>
+        <v>156</v>
       </c>
       <c r="R8" t="n">
-        <v>2083</v>
+        <v>632</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,56 +1228,56 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1587891622</t>
+          <t>1743697484</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1587891622</t>
+          <t>https://m.place.naver.com/place/1743697484</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>라이트짐 장산점</t>
+          <t>언로드 PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>busan91@naver.com</t>
+          <t>unloadpt@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1438-1740</t>
+          <t>0507-1320-4232</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산 해운대구 양운로 92 9층 라이트짐</t>
+          <t>부산 해운대구 우동1로20번길 27-10 3층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sOS9sPTf</t>
+          <t>https://open.kakao.com/o/s8bzzHmi</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w45b6h</t>
+          <t>https://talk.naver.com/ct/wzjd0hu</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>728</v>
+        <v>4</v>
       </c>
       <c r="Q9" t="n">
-        <v>446</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>1174</v>
+        <v>5</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,17 +1326,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1418968603</t>
+          <t>2024136684</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1418968603</t>
+          <t>https://m.place.naver.com/place/2024136684</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1348,29 +1348,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>마이애미짐 센텀점 24시헬스PT</t>
+          <t>태리짐 PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>miamigymnc@naver.com</t>
+          <t>ansth1@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1319-8441</t>
+          <t>0507-1419-2400</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산 해운대구 센텀중앙로 90 B1</t>
+          <t>부산 해운대구 마린시티3로 37 한일오르듀 3층 312호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/miamigymnc</t>
+          <t>https://blog.naver.com/ansth1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5v1em</t>
+          <t>https://talk.naver.com/ct/w5ijd7</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1409,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>297</v>
+        <v>50</v>
       </c>
       <c r="Q10" t="n">
-        <v>463</v>
+        <v>269</v>
       </c>
       <c r="R10" t="n">
-        <v>760</v>
+        <v>319</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,115 +1424,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1160428762</t>
+          <t>1346702700</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1160428762</t>
+          <t>https://m.place.naver.com/place/1346702700</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>언로드 PT</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>unloadpt@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1320-4232</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>부산 해운대구 우동1로20번길 27-10 3층</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://open.kakao.com/o/s8bzzHmi</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wzjd0hu</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2024136684</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2024136684</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/해운대_헬스장.xlsx
+++ b/naver-place-crawler/results_health/해운대_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,8 +426,8 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="33" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>마블피트니스 헬스&amp;PT 해운대점</t>
+          <t>우노짐 헬스&amp;PT 마린시티점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>hyoyoung0202@naver.com</t>
+          <t>unogym_1@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1384-2203</t>
+          <t>0507-1419-1786</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산 해운대구 해운대로469번길 8 2층</t>
+          <t>부산 해운대구 마린시티2로 33 104동 B107-1호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hyoyoung0202</t>
+          <t>https://www.instagram.com/uno_gym_3</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5tzkb</t>
+          <t>https://talk.naver.com/ct/wpkopem</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1461</v>
+        <v>20</v>
       </c>
       <c r="Q2" t="n">
-        <v>1413</v>
+        <v>6</v>
       </c>
       <c r="R2" t="n">
-        <v>2874</v>
+        <v>26</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1774469002</t>
+          <t>2066839617</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1774469002</t>
+          <t>https://m.place.naver.com/place/2066839617</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>마이애미짐 해운대점 24시헬스PT</t>
+          <t>마블피트니스 헬스&amp;PT 해운대점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>jeffkim94@naver.com</t>
+          <t>hyoyoung0202@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1469-0064</t>
+          <t>0507-1384-2203</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산 해운대구 해운대로 743 4층</t>
+          <t>부산 해운대구 해운대로469번길 8 2층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jeffkim94</t>
+          <t>https://blog.naver.com/hyoyoung0202</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4n1kz</t>
+          <t>https://talk.naver.com/ct/w5tzkb</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>430</v>
+        <v>1465</v>
       </c>
       <c r="Q3" t="n">
-        <v>956</v>
+        <v>1419</v>
       </c>
       <c r="R3" t="n">
-        <v>1386</v>
+        <v>2884</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1040976831</t>
+          <t>1774469002</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040976831</t>
+          <t>https://m.place.naver.com/place/1774469002</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>멋짐 헬스 &amp; PT 마린시티점</t>
+          <t>마이애미짐 해운대점 24시헬스PT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>mutgym_@naver.com</t>
+          <t>jeffkim94@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1380-2436</t>
+          <t>0507-1469-0064</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산 해운대구 해운대해변로 163 현대베네시티 베네치아상가 지하1층 b101호, b101-2호, b101-5호</t>
+          <t>부산 해운대구 해운대로 743 4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mutgym_</t>
+          <t>https://blog.naver.com/jeffkim94</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wayqe12</t>
+          <t>https://talk.naver.com/ct/w4n1kz</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>77</v>
+        <v>430</v>
       </c>
       <c r="Q4" t="n">
-        <v>214</v>
+        <v>957</v>
       </c>
       <c r="R4" t="n">
-        <v>291</v>
+        <v>1387</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2055602485</t>
+          <t>1040976831</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055602485</t>
+          <t>https://m.place.naver.com/place/1040976831</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="Q5" t="n">
         <v>445</v>
       </c>
       <c r="R5" t="n">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -956,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>쑥피트니스 해운대점</t>
+          <t>뉴피트니스 2호점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ssookfitness_hd@naver.com</t>
+          <t>rational12074@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1308-8420</t>
+          <t>0507-1478-3602</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산 해운대구 해운대로774번길 11 4층</t>
+          <t>부산 해운대구 세실로69번길 24 8층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ssookfitness_hd</t>
+          <t>https://www.instagram.com/new____fitness_2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4f0d6</t>
+          <t>https://talk.naver.com/ct/w4i0zg</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>393</v>
+        <v>175</v>
       </c>
       <c r="Q6" t="n">
-        <v>483</v>
+        <v>236</v>
       </c>
       <c r="R6" t="n">
-        <v>876</v>
+        <v>411</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,51 +1032,51 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1246026577</t>
+          <t>1020154888</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1246026577</t>
+          <t>https://m.place.naver.com/place/1020154888</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>마이애미짐 센텀점 24시헬스PT</t>
+          <t>쑥피트니스 해운대점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>miamigymnc@naver.com</t>
+          <t>ssookfitness_hd@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1319-8441</t>
+          <t>0507-1308-8420</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산 해운대구 센텀중앙로 90 B1</t>
+          <t>부산 해운대구 해운대로774번길 11 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/miamigymnc</t>
+          <t>https://blog.naver.com/ssookfitness_hd</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5v1em</t>
+          <t>https://talk.naver.com/ct/w4f0d6</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>302</v>
+        <v>397</v>
       </c>
       <c r="Q7" t="n">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="R7" t="n">
-        <v>774</v>
+        <v>881</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1130,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1160428762</t>
+          <t>1246026577</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1160428762</t>
+          <t>https://m.place.naver.com/place/1246026577</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1152,29 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>그래비티짐 해운대 장산점</t>
+          <t>마이애미짐 센텀점 24시헬스PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>acmilan0@naver.com</t>
+          <t>miamigymnc@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1397-0149</t>
+          <t>0507-1319-8441</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산 해운대구 해운대로 802 웅신시네아트 A동 6층</t>
+          <t>부산 해운대구 센텀중앙로 90 B1</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/acmilan0</t>
+          <t>https://blog.naver.com/miamigymnc</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4o8qo</t>
+          <t>https://talk.naver.com/ct/w5v1em</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>476</v>
+        <v>304</v>
       </c>
       <c r="Q8" t="n">
-        <v>156</v>
+        <v>474</v>
       </c>
       <c r="R8" t="n">
-        <v>632</v>
+        <v>778</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1743697484</t>
+          <t>1160428762</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1743697484</t>
+          <t>https://m.place.naver.com/place/1160428762</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1250,34 +1250,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>언로드 PT</t>
+          <t>그래비티짐 해운대 장산점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>unloadpt@naver.com</t>
+          <t>acmilan0@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1320-4232</t>
+          <t>0507-1397-0149</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산 해운대구 우동1로20번길 27-10 3층</t>
+          <t>부산 해운대구 해운대로 802 웅신시네아트 A동 6층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/s8bzzHmi</t>
+          <t>https://blog.naver.com/acmilan0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wzjd0hu</t>
+          <t>https://talk.naver.com/ct/w4o8qo</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>476</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>156</v>
       </c>
       <c r="R9" t="n">
-        <v>5</v>
+        <v>632</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,17 +1326,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2024136684</t>
+          <t>1743697484</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2024136684</t>
+          <t>https://m.place.naver.com/place/1743697484</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1348,93 +1348,191 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>태리짐 PT</t>
+          <t>언로드 PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ansth1@naver.com</t>
+          <t>unloadpt@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1419-2400</t>
+          <t>0507-1320-4232</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
+          <t>부산 해운대구 우동1로20번길 27-10 3층</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/s8bzzHmi</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wzjd0hu</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>5</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2024136684</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2024136684</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>태리짐 PT</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ansth1@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1419-2400</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>부산 해운대구 마린시티3로 37 한일오르듀 3층 312호</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>https://blog.naver.com/ansth1</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/w5ijd7</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
         <v>50</v>
       </c>
-      <c r="Q10" t="n">
-        <v>269</v>
-      </c>
-      <c r="R10" t="n">
-        <v>319</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
+      <c r="Q11" t="n">
+        <v>270</v>
+      </c>
+      <c r="R11" t="n">
+        <v>320</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
         <is>
           <t>1346702700</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1346702700</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/해운대_헬스장.xlsx
+++ b/naver-place-crawler/results_health/해운대_헬스장.xlsx
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="33" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
     <col width="44" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -679,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산 해운대구 해운대로469번길 8 2층</t>
+          <t>부산광역시 해운대구 해운대로469번길 8 2층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -704,14 +704,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5tzkb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -726,10 +722,10 @@
         <v>1465</v>
       </c>
       <c r="Q3" t="n">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="R3" t="n">
-        <v>2884</v>
+        <v>2885</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -777,7 +773,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산 해운대구 해운대로 743 4층</t>
+          <t>부산광역시 해운대구 해운대로 743 4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -802,14 +798,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4n1kz</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -858,29 +850,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>라이트짐 장산점</t>
+          <t>뉴피트니스 2호점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>busan91@naver.com</t>
+          <t>rational12074@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1438-1740</t>
+          <t>0507-1478-3602</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산 해운대구 양운로 92 9층 라이트짐</t>
+          <t>부산광역시 해운대구 세실로69번길 24 8층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sOS9sPTf</t>
+          <t>https://www.instagram.com/new____fitness_2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -900,17 +892,13 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w45b6h</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -919,13 +907,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>734</v>
+        <v>175</v>
       </c>
       <c r="Q5" t="n">
-        <v>445</v>
+        <v>236</v>
       </c>
       <c r="R5" t="n">
-        <v>1179</v>
+        <v>411</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +922,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1418968603</t>
+          <t>1020154888</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1418968603</t>
+          <t>https://m.place.naver.com/place/1020154888</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -956,29 +944,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>뉴피트니스 2호점</t>
+          <t>라이트짐 장산점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>rational12074@naver.com</t>
+          <t>busan91@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1478-3602</t>
+          <t>0507-1438-1740</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산 해운대구 세실로69번길 24 8층</t>
+          <t>부산광역시 해운대구 양운로 92 9층 라이트짐</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/new____fitness_2</t>
+          <t>https://open.kakao.com/o/sOS9sPTf</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -998,17 +986,13 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4i0zg</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1017,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>175</v>
+        <v>734</v>
       </c>
       <c r="Q6" t="n">
-        <v>236</v>
+        <v>444</v>
       </c>
       <c r="R6" t="n">
-        <v>411</v>
+        <v>1178</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1016,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1020154888</t>
+          <t>1418968603</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1020154888</t>
+          <t>https://m.place.naver.com/place/1418968603</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1071,7 +1055,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산 해운대구 해운대로774번길 11 4층</t>
+          <t>부산광역시 해운대구 해운대로774번길 11 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1096,14 +1080,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4f0d6</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1169,7 +1149,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산 해운대구 센텀중앙로 90 B1</t>
+          <t>부산광역시 해운대구 센텀중앙로 90 B1</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1194,14 +1174,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5v1em</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1267,7 +1243,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산 해운대구 해운대로 802 웅신시네아트 A동 6층</t>
+          <t>부산광역시 해운대구 해운대로 802 웅신시네아트 A동 6층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1292,14 +1268,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4o8qo</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>

--- a/naver-place-crawler/results_health/해운대_헬스장.xlsx
+++ b/naver-place-crawler/results_health/해운대_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="33" customWidth="1" min="7" max="7"/>
     <col width="44" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>우노짐 헬스&amp;PT 마린시티점</t>
+          <t>마블피트니스 헬스&amp;PT 해운대점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>unogym_1@naver.com</t>
+          <t>hyoyoung0202@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1419-1786</t>
+          <t>0507-1384-2203</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산 해운대구 마린시티2로 33 104동 B107-1호</t>
+          <t>부산 해운대구 해운대로469번길 8 2층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/uno_gym_3</t>
+          <t>https://blog.naver.com/hyoyoung0202</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wpkopem</t>
+          <t>https://talk.naver.com/ct/w5tzkb</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>20</v>
+        <v>1466</v>
       </c>
       <c r="Q2" t="n">
-        <v>6</v>
+        <v>1421</v>
       </c>
       <c r="R2" t="n">
-        <v>26</v>
+        <v>2887</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2066839617</t>
+          <t>1774469002</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2066839617</t>
+          <t>https://m.place.naver.com/place/1774469002</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>마블피트니스 헬스&amp;PT 해운대점</t>
+          <t>마이애미짐 해운대점 24시헬스PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>hyoyoung0202@naver.com</t>
+          <t>jeffkim94@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1384-2203</t>
+          <t>0507-1469-0064</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 해운대로469번길 8 2층</t>
+          <t>부산 해운대구 해운대로 743 4층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hyoyoung0202</t>
+          <t>https://blog.naver.com/jeffkim94</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -704,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4n1kz</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1465</v>
+        <v>430</v>
       </c>
       <c r="Q3" t="n">
-        <v>1420</v>
+        <v>957</v>
       </c>
       <c r="R3" t="n">
-        <v>2885</v>
+        <v>1387</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1774469002</t>
+          <t>1040976831</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1774469002</t>
+          <t>https://m.place.naver.com/place/1040976831</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -751,34 +755,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>마이애미짐 해운대점 24시헬스PT</t>
+          <t>뉴피트니스 2호점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>jeffkim94@naver.com</t>
+          <t>rational12074@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1469-0064</t>
+          <t>0507-1478-3602</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 해운대로 743 4층</t>
+          <t>부산 해운대구 세실로69번길 24 8층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jeffkim94</t>
+          <t>https://www.instagram.com/new____fitness_2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,15 +797,19 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4i0zg</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -813,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>430</v>
+        <v>175</v>
       </c>
       <c r="Q4" t="n">
-        <v>957</v>
+        <v>236</v>
       </c>
       <c r="R4" t="n">
-        <v>1387</v>
+        <v>411</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1040976831</t>
+          <t>1020154888</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040976831</t>
+          <t>https://m.place.naver.com/place/1020154888</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -850,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>뉴피트니스 2호점</t>
+          <t>라이트짐 장산점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>rational12074@naver.com</t>
+          <t>busan91@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1478-3602</t>
+          <t>0507-1438-1740</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 세실로69번길 24 8층</t>
+          <t>부산 해운대구 양운로 92 9층 라이트짐</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/new____fitness_2</t>
+          <t>https://open.kakao.com/o/sOS9sPTf</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -892,13 +900,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w45b6h</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -907,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>175</v>
+        <v>734</v>
       </c>
       <c r="Q5" t="n">
-        <v>236</v>
+        <v>444</v>
       </c>
       <c r="R5" t="n">
-        <v>411</v>
+        <v>1178</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1020154888</t>
+          <t>1418968603</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1020154888</t>
+          <t>https://m.place.naver.com/place/1418968603</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -939,34 +951,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>라이트짐 장산점</t>
+          <t>마이애미짐 센텀점 24시헬스PT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>busan91@naver.com</t>
+          <t>miamigymnc@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1438-1740</t>
+          <t>0507-1319-8441</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 양운로 92 9층 라이트짐</t>
+          <t>부산 해운대구 센텀중앙로 90 B1</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sOS9sPTf</t>
+          <t>https://blog.naver.com/miamigymnc</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -981,18 +993,22 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5v1em</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -1001,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>734</v>
+        <v>304</v>
       </c>
       <c r="Q6" t="n">
-        <v>444</v>
+        <v>474</v>
       </c>
       <c r="R6" t="n">
-        <v>1178</v>
+        <v>778</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1016,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1418968603</t>
+          <t>1160428762</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1418968603</t>
+          <t>https://m.place.naver.com/place/1160428762</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1038,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>쑥피트니스 해운대점</t>
+          <t>쑥피트니스 장산점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ssookfitness_hd@naver.com</t>
+          <t>hgym_js2@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1308-8420</t>
+          <t>0507-1321-1316</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 해운대로774번길 11 4층</t>
+          <t>부산 해운대구 좌동순환로 245 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ssookfitness_hd</t>
+          <t>https://blog.naver.com/hgym_js2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1080,10 +1096,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40ib3</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1095,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>397</v>
+        <v>500</v>
       </c>
       <c r="Q7" t="n">
-        <v>484</v>
+        <v>595</v>
       </c>
       <c r="R7" t="n">
-        <v>881</v>
+        <v>1095</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1246026577</t>
+          <t>1198390497</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1246026577</t>
+          <t>https://m.place.naver.com/place/1198390497</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1132,29 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>마이애미짐 센텀점 24시헬스PT</t>
+          <t>그래비티짐 해운대 장산점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>miamigymnc@naver.com</t>
+          <t>acmilan0@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1319-8441</t>
+          <t>0507-1397-0149</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 센텀중앙로 90 B1</t>
+          <t>부산 해운대구 해운대로 802 웅신시네아트 A동 6층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/miamigymnc</t>
+          <t>https://blog.naver.com/acmilan0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1174,10 +1194,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4o8qo</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1189,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>304</v>
+        <v>477</v>
       </c>
       <c r="Q8" t="n">
-        <v>474</v>
+        <v>156</v>
       </c>
       <c r="R8" t="n">
-        <v>778</v>
+        <v>633</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1160428762</t>
+          <t>1743697484</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1160428762</t>
+          <t>https://m.place.naver.com/place/1743697484</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1226,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>그래비티짐 해운대 장산점</t>
+          <t>태리짐 PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>acmilan0@naver.com</t>
+          <t>ansth1@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1397-0149</t>
+          <t>0507-1419-2400</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 해운대로 802 웅신시네아트 A동 6층</t>
+          <t>부산 해운대구 마린시티3로 37 한일오르듀 3층 312호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/acmilan0</t>
+          <t>https://blog.naver.com/ansth1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1268,10 +1292,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ijd7</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1283,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>476</v>
+        <v>50</v>
       </c>
       <c r="Q9" t="n">
-        <v>156</v>
+        <v>270</v>
       </c>
       <c r="R9" t="n">
-        <v>632</v>
+        <v>320</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,211 +1326,15 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1743697484</t>
+          <t>1346702700</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1743697484</t>
+          <t>https://m.place.naver.com/place/1346702700</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>언로드 PT</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>unloadpt@naver.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1320-4232</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>부산 해운대구 우동1로20번길 27-10 3층</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>https://open.kakao.com/o/s8bzzHmi</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wzjd0hu</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>5</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>2024136684</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2024136684</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>태리짐 PT</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>ansth1@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1419-2400</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>부산 해운대구 마린시티3로 37 한일오르듀 3층 312호</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/ansth1</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5ijd7</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>270</v>
-      </c>
-      <c r="R11" t="n">
-        <v>320</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>1346702700</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1346702700</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/해운대_헬스장.xlsx
+++ b/naver-place-crawler/results_health/해운대_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="33" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -569,7 +569,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>hyoyoung0202@naver.com</t>
+          <t>hyewon9888@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hyoyoung0202</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="Q2" t="n">
         <v>1421</v>
       </c>
       <c r="R2" t="n">
-        <v>2887</v>
+        <v>2886</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jeffkim94</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/new____fitness_2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -944,41 +944,41 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>마이애미짐 센텀점 24시헬스PT</t>
+          <t>쑥피트니스 해운대점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>miamigymnc@naver.com</t>
+          <t>ssookfitness_hd@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1319-8441</t>
+          <t>0507-1308-8420</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산 해운대구 센텀중앙로 90 B1</t>
+          <t>부산 해운대구 해운대로774번길 11 4층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/miamigymnc</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -988,12 +988,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5v1em</t>
+          <t>https://talk.naver.com/ct/w4f0d6</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>304</v>
+        <v>397</v>
       </c>
       <c r="Q6" t="n">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="R6" t="n">
-        <v>778</v>
+        <v>881</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,51 +1032,51 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1160428762</t>
+          <t>1246026577</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1160428762</t>
+          <t>https://m.place.naver.com/place/1246026577</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>쑥피트니스 장산점</t>
+          <t>마이애미짐 센텀점 24시헬스PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>hgym_js2@naver.com</t>
+          <t>miamigymnc@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1321-1316</t>
+          <t>0507-1319-8441</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산 해운대구 좌동순환로 245 4층</t>
+          <t>부산 해운대구 센텀중앙로 90 B1</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hgym_js2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40ib3</t>
+          <t>https://talk.naver.com/ct/w5v1em</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>500</v>
+        <v>304</v>
       </c>
       <c r="Q7" t="n">
-        <v>595</v>
+        <v>474</v>
       </c>
       <c r="R7" t="n">
-        <v>1095</v>
+        <v>778</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1130,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1198390497</t>
+          <t>1160428762</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1198390497</t>
+          <t>https://m.place.naver.com/place/1160428762</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1216,10 +1216,10 @@
         <v>477</v>
       </c>
       <c r="Q8" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="R8" t="n">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1250,93 +1250,191 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>태리짐 PT</t>
+          <t>언로드 PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ansth1@naver.com</t>
+          <t>unloadpt@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1419-2400</t>
+          <t>0507-1320-4232</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
+          <t>부산 해운대구 우동1로20번길 27-10 3층</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/s8bzzHmi</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wzjd0hu</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>5</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2024136684</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2024136684</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>태리짐 PT</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ansth1@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1419-2400</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>부산 해운대구 마린시티3로 37 한일오르듀 3층 312호</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>https://blog.naver.com/ansth1</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/w5ijd7</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
         <v>50</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q10" t="n">
         <v>270</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R10" t="n">
         <v>320</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
         <is>
           <t>1346702700</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1346702700</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/해운대_헬스장.xlsx
+++ b/naver-place-crawler/results_health/해운대_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="33" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
     <col width="44" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산 해운대구 해운대로469번길 8 2층</t>
+          <t>부산광역시 해운대구 해운대로469번길 8 2층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -704,14 +704,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5tzkb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +719,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="Q3" t="n">
         <v>1422</v>
       </c>
       <c r="R3" t="n">
-        <v>2889</v>
+        <v>2891</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -777,7 +773,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산 해운대구 세실로69번길 24 8층</t>
+          <t>부산광역시 해운대구 세실로69번길 24 8층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -802,14 +798,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4i0zg</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -846,7 +838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -875,7 +867,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산 해운대구 해운대로 743 4층</t>
+          <t>부산광역시 해운대구 해운대로 743 4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -900,14 +892,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4n1kz</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -944,7 +932,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -973,7 +961,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산 해운대구 양운로 92 9층 라이트짐</t>
+          <t>부산광역시 해운대구 양운로 92 9층 라이트짐</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -983,7 +971,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -998,14 +986,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w45b6h</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>O</t>
@@ -1017,13 +1001,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="Q6" t="n">
         <v>444</v>
       </c>
       <c r="R6" t="n">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1042,41 +1026,41 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>마이애미짐 센텀점 24시헬스PT</t>
+          <t>쑥피트니스 장산점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>miamigymnc@naver.com</t>
+          <t>hgym_js2@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1319-8441</t>
+          <t>0507-1321-1316</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산 해운대구 센텀중앙로 90 B1</t>
+          <t>부산 해운대구 좌동순환로 245 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/miamigymnc</t>
+          <t>https://blog.naver.com/hgym_js2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1101,7 +1085,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5v1em</t>
+          <t>https://talk.naver.com/ct/w40ib3</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1099,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>304</v>
+        <v>500</v>
       </c>
       <c r="Q7" t="n">
-        <v>474</v>
+        <v>596</v>
       </c>
       <c r="R7" t="n">
-        <v>778</v>
+        <v>1096</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,51 +1114,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1160428762</t>
+          <t>1198390497</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1160428762</t>
+          <t>https://m.place.naver.com/place/1198390497</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>쑥피트니스 장산점</t>
+          <t>그래비티짐 해운대 장산점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>hgym_js2@naver.com</t>
+          <t>acmilan0@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1321-1316</t>
+          <t>0507-1397-0149</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산 해운대구 좌동순환로 245 4층</t>
+          <t>부산광역시 해운대구 해운대로 802 웅신시네아트 A동 6층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hgym_js2</t>
+          <t>https://blog.naver.com/acmilan0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1194,14 +1178,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w40ib3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1213,13 +1193,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>500</v>
+        <v>477</v>
       </c>
       <c r="Q8" t="n">
-        <v>596</v>
+        <v>156</v>
       </c>
       <c r="R8" t="n">
-        <v>1096</v>
+        <v>633</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,17 +1208,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1198390497</t>
+          <t>1743697484</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1198390497</t>
+          <t>https://m.place.naver.com/place/1743697484</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1230,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>그래비티짐 해운대 장산점</t>
+          <t>태리짐 PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>acmilan0@naver.com</t>
+          <t>ansth1@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1397-0149</t>
+          <t>0507-1419-2400</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산 해운대구 해운대로 802 웅신시네아트 A동 6층</t>
+          <t>부산 해운대구 마린시티3로 37 한일오르듀 3층 312호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/acmilan0</t>
+          <t>https://blog.naver.com/ansth1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1297,7 +1277,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4o8qo</t>
+          <t>https://talk.naver.com/ct/w5ijd7</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,13 +1291,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>477</v>
+        <v>50</v>
       </c>
       <c r="Q9" t="n">
-        <v>156</v>
+        <v>270</v>
       </c>
       <c r="R9" t="n">
-        <v>633</v>
+        <v>320</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,17 +1306,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1743697484</t>
+          <t>1346702700</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1743697484</t>
+          <t>https://m.place.naver.com/place/1346702700</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1348,34 +1328,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>태리짐 PT</t>
+          <t>더바른교정재활센터 해운대본점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ansth1@naver.com</t>
+          <t>j1024up@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1419-2400</t>
+          <t>0507-1482-1689</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산 해운대구 마린시티3로 37 한일오르듀 3층 312호</t>
+          <t>부산 해운대구 해운대로 794 엘리움 빌딩 3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ansth1</t>
+          <t>http://pf.kakao.com/_pHxaws/chat</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1385,37 +1365,33 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5ijd7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="Q10" t="n">
-        <v>270</v>
+        <v>33</v>
       </c>
       <c r="R10" t="n">
-        <v>320</v>
+        <v>68</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,17 +1400,115 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1346702700</t>
+          <t>1300227430</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1346702700</t>
+          <t>https://m.place.naver.com/place/1300227430</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>에이치앤케이짐</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>hyup1016@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1347-0567</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>부산 해운대구 좌동로10번길 15 2층 에이치앤케이짐</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hyup1016</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcegdk</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>102</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>204</v>
+      </c>
+      <c r="R11" t="n">
+        <v>306</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>31543040</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/31543040</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/해운대_헬스장.xlsx
+++ b/naver-place-crawler/results_health/해운대_헬스장.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="33" customWidth="1" min="7" max="7"/>
     <col width="44" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -679,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 해운대로469번길 8 2층</t>
+          <t>부산 해운대구 해운대로469번길 8 2층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -704,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5tzkb</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -719,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1469</v>
+        <v>1472</v>
       </c>
       <c r="Q3" t="n">
-        <v>1422</v>
+        <v>1425</v>
       </c>
       <c r="R3" t="n">
-        <v>2891</v>
+        <v>2897</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -773,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 세실로69번길 24 8층</t>
+          <t>부산 해운대구 세실로69번길 24 8층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -798,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4i0zg</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -867,7 +875,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 해운대로 743 4층</t>
+          <t>부산 해운대구 해운대로 743 4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -892,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4n1kz</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -910,10 +922,10 @@
         <v>430</v>
       </c>
       <c r="Q5" t="n">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="R5" t="n">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -961,7 +973,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 양운로 92 9층 라이트짐</t>
+          <t>부산 해운대구 양운로 92 9층 라이트짐</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -986,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w45b6h</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>O</t>
@@ -1038,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>쑥피트니스 장산점</t>
+          <t>쑥피트니스 해운대점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>hgym_js2@naver.com</t>
+          <t>ssookfitness_hd@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1321-1316</t>
+          <t>0507-1308-8420</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산 해운대구 좌동순환로 245 4층</t>
+          <t>부산 해운대구 해운대로774번길 11 4층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hgym_js2</t>
+          <t>https://blog.naver.com/ssookfitness_hd</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1085,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40ib3</t>
+          <t>https://talk.naver.com/ct/w4f0d6</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1099,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>500</v>
+        <v>398</v>
       </c>
       <c r="Q7" t="n">
-        <v>596</v>
+        <v>485</v>
       </c>
       <c r="R7" t="n">
-        <v>1096</v>
+        <v>883</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1114,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1198390497</t>
+          <t>1246026577</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1198390497</t>
+          <t>https://m.place.naver.com/place/1246026577</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1136,29 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>그래비티짐 해운대 장산점</t>
+          <t>마이애미짐 센텀점 24시헬스PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>acmilan0@naver.com</t>
+          <t>miamigymnc@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1397-0149</t>
+          <t>0507-1319-8441</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 해운대로 802 웅신시네아트 A동 6층</t>
+          <t>부산 해운대구 센텀중앙로 90 B1</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/acmilan0</t>
+          <t>https://blog.naver.com/miamigymnc</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1178,10 +1194,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5v1em</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1193,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>477</v>
+        <v>304</v>
       </c>
       <c r="Q8" t="n">
-        <v>156</v>
+        <v>476</v>
       </c>
       <c r="R8" t="n">
-        <v>633</v>
+        <v>780</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1208,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1743697484</t>
+          <t>1160428762</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1743697484</t>
+          <t>https://m.place.naver.com/place/1160428762</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1230,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>태리짐 PT</t>
+          <t>그래비티짐 해운대 장산점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ansth1@naver.com</t>
+          <t>acmilan0@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1419-2400</t>
+          <t>0507-1397-0149</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산 해운대구 마린시티3로 37 한일오르듀 3층 312호</t>
+          <t>부산 해운대구 해운대로 802 웅신시네아트 A동 6층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ansth1</t>
+          <t>https://blog.naver.com/acmilan0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1277,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5ijd7</t>
+          <t>https://talk.naver.com/ct/w4o8qo</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1291,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>50</v>
+        <v>477</v>
       </c>
       <c r="Q9" t="n">
-        <v>270</v>
+        <v>158</v>
       </c>
       <c r="R9" t="n">
-        <v>320</v>
+        <v>635</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1306,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1346702700</t>
+          <t>1743697484</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1346702700</t>
+          <t>https://m.place.naver.com/place/1743697484</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1328,34 +1348,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>더바른교정재활센터 해운대본점</t>
+          <t>태리짐 PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>j1024up@naver.com</t>
+          <t>ansth1@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1482-1689</t>
+          <t>0507-1419-2400</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산 해운대구 해운대로 794 엘리움 빌딩 3층</t>
+          <t>부산 해운대구 마린시티3로 37 한일오르듀 3층 312호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_pHxaws/chat</t>
+          <t>https://blog.naver.com/ansth1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1365,33 +1385,37 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ijd7</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="Q10" t="n">
-        <v>33</v>
+        <v>270</v>
       </c>
       <c r="R10" t="n">
-        <v>68</v>
+        <v>320</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1400,113 +1424,15 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1300227430</t>
+          <t>1346702700</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1300227430</t>
+          <t>https://m.place.naver.com/place/1346702700</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>에이치앤케이짐</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>hyup1016@naver.com</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1347-0567</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>부산 해운대구 좌동로10번길 15 2층 에이치앤케이짐</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/hyup1016</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcegdk</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>102</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>204</v>
-      </c>
-      <c r="R11" t="n">
-        <v>306</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>31543040</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/31543040</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>

--- a/naver-place-crawler/results_health/해운대_헬스장.xlsx
+++ b/naver-place-crawler/results_health/해운대_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="Q3" t="n">
         <v>1425</v>
       </c>
       <c r="R3" t="n">
-        <v>2897</v>
+        <v>2898</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -983,7 +983,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="Q6" t="n">
         <v>444</v>
       </c>
       <c r="R6" t="n">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="Q7" t="n">
         <v>485</v>
       </c>
       <c r="R7" t="n">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1348,93 +1348,191 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>태리짐 PT</t>
+          <t>언로드 PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ansth1@naver.com</t>
+          <t>unloadpt@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1419-2400</t>
+          <t>0507-1320-4232</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
+          <t>부산 해운대구 우동1로20번길 27-10 3층</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/s8bzzHmi</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wzjd0hu</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>5</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>2024136684</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2024136684</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>태리짐 PT</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ansth1@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1419-2400</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>부산 해운대구 마린시티3로 37 한일오르듀 3층 312호</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>https://blog.naver.com/ansth1</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/w5ijd7</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
         <v>50</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q11" t="n">
         <v>270</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R11" t="n">
         <v>320</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
         <is>
           <t>1346702700</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1346702700</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/해운대_헬스장.xlsx
+++ b/naver-place-crawler/results_health/해운대_헬스장.xlsx
@@ -1412,10 +1412,10 @@
         <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
